--- a/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>中转报关单号</t>
   </si>
@@ -56,9 +56,6 @@
     <t>包裹总重量</t>
   </si>
   <si>
-    <t>重量单位</t>
-  </si>
-  <si>
     <t>销售单号</t>
   </si>
   <si>
@@ -110,16 +107,13 @@
     <t>{.packageTotalWeight}</t>
   </si>
   <si>
-    <t>{.weightUnit}</t>
-  </si>
-  <si>
     <t>{.soCode}</t>
   </si>
   <si>
     <t>{.logisticsChannelName}</t>
   </si>
   <si>
-    <t>{.trackingNo}</t>
+    <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.uploadOrderStatusName}</t>
@@ -1108,7 +1102,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
@@ -1118,20 +1112,19 @@
     <col min="5" max="5" width="19.25" customWidth="1"/>
     <col min="6" max="6" width="19.625" customWidth="1"/>
     <col min="7" max="7" width="9.25" customWidth="1"/>
-    <col min="9" max="9" width="7.875" customWidth="1"/>
-    <col min="10" max="10" width="16.75" customWidth="1"/>
-    <col min="11" max="11" width="20.625" customWidth="1"/>
-    <col min="12" max="12" width="16.625" customWidth="1"/>
-    <col min="13" max="13" width="12.625" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="11.875" customWidth="1"/>
-    <col min="17" max="17" width="8.5" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="9.375" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="9" max="9" width="16.75" customWidth="1"/>
+    <col min="10" max="10" width="20.625" customWidth="1"/>
+    <col min="11" max="11" width="16.625" customWidth="1"/>
+    <col min="12" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="11.875" customWidth="1"/>
+    <col min="16" max="16" width="8.5" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="9.375" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1183,64 +1176,58 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>中转报关单号</t>
   </si>
@@ -38,7 +38,10 @@
     <t>预计中转日期</t>
   </si>
   <si>
-    <t>上传状态(批次)</t>
+    <t>订单预报(批次)</t>
+  </si>
+  <si>
+    <t>入库预报状态</t>
   </si>
   <si>
     <t>发货物流商中文</t>
@@ -90,6 +93,9 @@
   </si>
   <si>
     <t>{.uploadBatchStatusName}</t>
+  </si>
+  <si>
+    <t>{.instockForecastStatusName}</t>
   </si>
   <si>
     <t>{.deliveryLogisticsSupplierName}</t>
@@ -1102,29 +1108,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
     <col min="2" max="2" width="11.125" customWidth="1"/>
-    <col min="3" max="3" width="13.25" customWidth="1"/>
-    <col min="4" max="4" width="18.375" customWidth="1"/>
-    <col min="5" max="5" width="19.25" customWidth="1"/>
-    <col min="6" max="6" width="19.625" customWidth="1"/>
-    <col min="7" max="7" width="9.25" customWidth="1"/>
-    <col min="9" max="9" width="16.75" customWidth="1"/>
-    <col min="10" max="10" width="20.625" customWidth="1"/>
-    <col min="11" max="11" width="16.625" customWidth="1"/>
-    <col min="12" max="12" width="12.625" customWidth="1"/>
-    <col min="13" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="11.875" customWidth="1"/>
-    <col min="16" max="16" width="8.5" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="9.375" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="3" max="4" width="13.25" customWidth="1"/>
+    <col min="5" max="5" width="18.375" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="7" max="7" width="19.625" customWidth="1"/>
+    <col min="8" max="8" width="9.25" customWidth="1"/>
+    <col min="10" max="10" width="16.75" customWidth="1"/>
+    <col min="11" max="11" width="20.625" customWidth="1"/>
+    <col min="12" max="12" width="16.625" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="15" max="15" width="11.875" customWidth="1"/>
+    <col min="17" max="17" width="8.5" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="9.375" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,58 +1182,64 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>中转报关单号</t>
   </si>
@@ -80,6 +80,9 @@
     <t>失败原因</t>
   </si>
   <si>
+    <t>入库失败原因</t>
+  </si>
+  <si>
     <t>创建人</t>
   </si>
   <si>
@@ -132,6 +135,9 @@
   </si>
   <si>
     <t>{.failureReason}</t>
+  </si>
+  <si>
+    <t>{.instockForecastRemark}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1108,7 +1114,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
@@ -1124,13 +1130,13 @@
     <col min="13" max="13" width="12.625" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
     <col min="15" max="15" width="11.875" customWidth="1"/>
-    <col min="17" max="17" width="8.5" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="9.375" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="17" max="18" width="8.5" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="9.375" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,61 +1191,67 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>中转报关单号</t>
   </si>
@@ -38,6 +38,9 @@
     <t>预计中转日期</t>
   </si>
   <si>
+    <t>入库预报日期</t>
+  </si>
+  <si>
     <t>订单预报(批次)</t>
   </si>
   <si>
@@ -93,6 +96,9 @@
   </si>
   <si>
     <t>{.planTransferDate}</t>
+  </si>
+  <si>
+    <t>{.instockForcastDate}</t>
   </si>
   <si>
     <t>{.uploadBatchStatusName}</t>
@@ -1114,29 +1120,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
-    <col min="2" max="2" width="11.125" customWidth="1"/>
-    <col min="3" max="4" width="13.25" customWidth="1"/>
-    <col min="5" max="5" width="18.375" customWidth="1"/>
-    <col min="6" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="7" width="19.625" customWidth="1"/>
-    <col min="8" max="8" width="9.25" customWidth="1"/>
-    <col min="10" max="10" width="16.75" customWidth="1"/>
-    <col min="11" max="11" width="20.625" customWidth="1"/>
-    <col min="12" max="12" width="16.625" customWidth="1"/>
-    <col min="13" max="13" width="12.625" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="11.875" customWidth="1"/>
-    <col min="17" max="18" width="8.5" customWidth="1"/>
-    <col min="19" max="19" width="18" customWidth="1"/>
-    <col min="20" max="20" width="9.375" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="2" max="3" width="11.125" customWidth="1"/>
+    <col min="4" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="18.375" customWidth="1"/>
+    <col min="7" max="7" width="19.25" customWidth="1"/>
+    <col min="8" max="8" width="19.625" customWidth="1"/>
+    <col min="9" max="9" width="9.25" customWidth="1"/>
+    <col min="11" max="11" width="16.75" customWidth="1"/>
+    <col min="12" max="12" width="20.625" customWidth="1"/>
+    <col min="13" max="13" width="16.625" customWidth="1"/>
+    <col min="14" max="14" width="12.625" customWidth="1"/>
+    <col min="15" max="15" width="9" customWidth="1"/>
+    <col min="16" max="16" width="11.875" customWidth="1"/>
+    <col min="18" max="19" width="8.5" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="9.375" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1194,64 +1200,70 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:20">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
     <t>上传状态(订单)</t>
   </si>
   <si>
-    <t>出库状态</t>
+    <t>出库状态(我司)</t>
   </si>
   <si>
     <t>中转状态</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
@@ -98,7 +98,7 @@
     <t>{.planTransferDate}</t>
   </si>
   <si>
-    <t>{.instockForcastDate}</t>
+    <t>{.instockForecastDate}</t>
   </si>
   <si>
     <t>{.uploadBatchStatusName}</t>

--- a/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/transferDeclare.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>中转报关单号</t>
   </si>
@@ -65,6 +65,9 @@
     <t>销售单号</t>
   </si>
   <si>
+    <t>组包单号</t>
+  </si>
+  <si>
     <t>物流渠道中文</t>
   </si>
   <si>
@@ -123,6 +126,9 @@
   </si>
   <si>
     <t>{.soCode}</t>
+  </si>
+  <si>
+    <t>{.packageForecastCode}</t>
   </si>
   <si>
     <t>{.logisticsChannelName}</t>
@@ -1120,7 +1126,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
@@ -1130,19 +1136,19 @@
     <col min="7" max="7" width="19.25" customWidth="1"/>
     <col min="8" max="8" width="19.625" customWidth="1"/>
     <col min="9" max="9" width="9.25" customWidth="1"/>
-    <col min="11" max="11" width="16.75" customWidth="1"/>
-    <col min="12" max="12" width="20.625" customWidth="1"/>
-    <col min="13" max="13" width="16.625" customWidth="1"/>
-    <col min="14" max="14" width="12.625" customWidth="1"/>
-    <col min="15" max="15" width="9" customWidth="1"/>
-    <col min="16" max="16" width="11.875" customWidth="1"/>
-    <col min="18" max="19" width="8.5" customWidth="1"/>
-    <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="11" max="12" width="16.75" customWidth="1"/>
+    <col min="13" max="13" width="20.625" customWidth="1"/>
+    <col min="14" max="14" width="16.625" customWidth="1"/>
+    <col min="15" max="15" width="12.625" customWidth="1"/>
+    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="17" max="17" width="11.875" customWidth="1"/>
+    <col min="19" max="20" width="8.5" customWidth="1"/>
+    <col min="21" max="21" width="18" customWidth="1"/>
+    <col min="22" max="22" width="9.375" customWidth="1"/>
+    <col min="23" max="23" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1203,67 +1209,73 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
